--- a/static/data/exports/Retro_CG_GE_2009.xlsx
+++ b/static/data/exports/Retro_CG_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_CG_GE_2009.xlsx
+++ b/static/data/exports/Retro_CG_GE_2009.xlsx
@@ -576,6 +576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>60</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>56</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>69</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>37</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>67</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +951,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>36</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>46</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>43</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1176,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>31</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1251,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>63</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>43</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>52</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1476,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>34</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1551,19 @@
           <t>AD</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>43</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>60</v>
+      </c>
       <c r="R16" t="n">
         <v>6</v>
       </c>
@@ -1503,6 +1698,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>56</v>
+      </c>
       <c r="R17" t="n">
         <v>6</v>
       </c>
@@ -1562,6 +1770,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>69</v>
+      </c>
       <c r="R18" t="n">
         <v>6</v>
       </c>
@@ -1621,6 +1842,19 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>37</v>
+      </c>
       <c r="R19" t="n">
         <v>6</v>
       </c>
@@ -1680,6 +1914,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>67</v>
+      </c>
       <c r="R20" t="n">
         <v>6</v>
       </c>
@@ -1739,6 +1986,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>36</v>
+      </c>
       <c r="R21" t="n">
         <v>6</v>
       </c>
@@ -1798,6 +2058,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>46</v>
+      </c>
       <c r="R22" t="n">
         <v>6</v>
       </c>
@@ -1857,6 +2130,19 @@
           <t>AD</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>43</v>
+      </c>
       <c r="R23" t="n">
         <v>6</v>
       </c>
@@ -1916,6 +2202,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>43</v>
+      </c>
       <c r="R24" t="n">
         <v>6</v>
       </c>
@@ -1975,6 +2274,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>31</v>
+      </c>
       <c r="R25" t="n">
         <v>6</v>
       </c>
@@ -2034,6 +2346,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>63</v>
+      </c>
       <c r="R26" t="n">
         <v>6</v>
       </c>
@@ -2093,6 +2418,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>52</v>
+      </c>
       <c r="R27" t="n">
         <v>6</v>
       </c>
@@ -2152,6 +2490,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>34</v>
+      </c>
       <c r="R28" t="n">
         <v>6</v>
       </c>
@@ -2211,6 +2562,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>43</v>
+      </c>
       <c r="R29" t="n">
         <v>6</v>
       </c>
@@ -2270,6 +2634,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>60</v>
+      </c>
       <c r="R30" t="n">
         <v>6</v>
       </c>
@@ -2329,6 +2706,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>56</v>
+      </c>
       <c r="R31" t="n">
         <v>6</v>
       </c>
@@ -2388,6 +2778,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>69</v>
+      </c>
       <c r="R32" t="n">
         <v>6</v>
       </c>
@@ -2447,6 +2850,19 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>37</v>
+      </c>
       <c r="R33" t="n">
         <v>6</v>
       </c>
@@ -2506,6 +2922,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>67</v>
+      </c>
       <c r="R34" t="n">
         <v>6</v>
       </c>
@@ -2565,6 +2994,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>31</v>
+      </c>
       <c r="R35" t="n">
         <v>6</v>
       </c>
@@ -2624,6 +3066,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>46</v>
+      </c>
       <c r="R36" t="n">
         <v>6</v>
       </c>
@@ -2683,6 +3138,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>36</v>
+      </c>
       <c r="R37" t="n">
         <v>6</v>
       </c>
@@ -2742,6 +3210,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>43</v>
+      </c>
       <c r="R38" t="n">
         <v>6</v>
       </c>
@@ -2801,6 +3282,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>43</v>
+      </c>
       <c r="R39" t="n">
         <v>6</v>
       </c>
@@ -2860,6 +3354,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>63</v>
+      </c>
       <c r="R40" t="n">
         <v>6</v>
       </c>
@@ -2919,6 +3426,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>52</v>
+      </c>
       <c r="R41" t="n">
         <v>6</v>
       </c>
@@ -2978,6 +3498,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>34</v>
+      </c>
       <c r="R42" t="n">
         <v>6</v>
       </c>
@@ -3037,6 +3570,19 @@
           <t>AD</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>43</v>
+      </c>
       <c r="R43" t="n">
         <v>6</v>
       </c>
@@ -3096,6 +3642,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>60</v>
+      </c>
       <c r="R44" t="n">
         <v>6</v>
       </c>
@@ -3155,6 +3714,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>56</v>
+      </c>
       <c r="R45" t="n">
         <v>6</v>
       </c>
@@ -3214,6 +3786,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>69</v>
+      </c>
       <c r="R46" t="n">
         <v>6</v>
       </c>
@@ -3273,6 +3858,19 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>37</v>
+      </c>
       <c r="R47" t="n">
         <v>6</v>
       </c>
@@ -3332,6 +3930,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>67</v>
+      </c>
       <c r="R48" t="n">
         <v>6</v>
       </c>
@@ -3391,6 +4002,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>36</v>
+      </c>
       <c r="R49" t="n">
         <v>6</v>
       </c>
@@ -3450,6 +4074,19 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>31</v>
+      </c>
       <c r="R50" t="n">
         <v>6</v>
       </c>
@@ -3509,6 +4146,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>46</v>
+      </c>
       <c r="R51" t="n">
         <v>6</v>
       </c>
@@ -3568,6 +4218,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>43</v>
+      </c>
       <c r="R52" t="n">
         <v>6</v>
       </c>
@@ -3627,6 +4290,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>43</v>
+      </c>
       <c r="R53" t="n">
         <v>6</v>
       </c>
@@ -3686,6 +4362,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>63</v>
+      </c>
       <c r="R54" t="n">
         <v>6</v>
       </c>
@@ -3745,6 +4434,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>34</v>
+      </c>
       <c r="R55" t="n">
         <v>6</v>
       </c>
@@ -3804,6 +4506,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>52</v>
+      </c>
       <c r="R56" t="n">
         <v>6</v>
       </c>
@@ -3862,6 +4577,19 @@
         <is>
           <t>AD</t>
         </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>43</v>
       </c>
       <c r="R57" t="n">
         <v>6</v>
